--- a/sampleprojects/TaxReturn/excel/states/SC.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/SC.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>DT: SC Military Retirement Exclusion</t>
   </si>
@@ -341,7 +341,10 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>SC taxable income after standard deduction</t>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>SC taxable income after standard deduction. Declared access=r while SC_dt.xml writes it; the core EDD declared the same field rw and won the merge, which is what made it work (#1109).</t>
   </si>
 </sst>
 </file>
@@ -3665,10 +3668,10 @@
         <v>14</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>14</v>
